--- a/ig/DM_FINESS_New/CodeSystem-tre-r427-type-adresse.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r427-type-adresse.xlsx
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Type d'adresse postale.</t>
+    <t>Type d'adresse postale tel que "Adresse du domicile", "Adresse de livraison" pour une personne physique.</t>
   </si>
   <si>
     <t>Purpose</t>
